--- a/项目文档/excel版遥测大表草稿/固定地址参数注入2.xlsx
+++ b/项目文档/excel版遥测大表草稿/固定地址参数注入2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codex Workspace\02_Projects\项目文档\excel版遥测大表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codex Workspace\04_projects\项目文档\excel版遥测大表草稿\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA321F38-68E2-40B9-80F9-14A31780EE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D7543C-C055-4913-87FD-B9E2AD76A7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="158">
   <si>
     <t>序号</t>
   </si>
@@ -44,10 +44,6 @@
   </si>
   <si>
     <t>参数名称</t>
-  </si>
-  <si>
-    <t>数据域偏移
-data_offset</t>
   </si>
   <si>
     <t>位偏移
@@ -58,10 +54,6 @@
 bit_length</t>
   </si>
   <si>
-    <t>数据类型
-type</t>
-  </si>
-  <si>
     <t>标识符</t>
   </si>
   <si>
@@ -301,29 +293,10 @@
     <t>TCT4096</t>
   </si>
   <si>
-    <t>字节序
-endian</t>
-  </si>
-  <si>
-    <t>小数位数
-decimal_places</t>
-  </si>
-  <si>
-    <t>单位
-unit</t>
-  </si>
-  <si>
-    <t>big</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指令码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>层级</t>
-  </si>
-  <si>
     <t>区域</t>
   </si>
   <si>
@@ -336,24 +309,9 @@
     <t>说明</t>
   </si>
   <si>
-    <t>数据包</t>
-  </si>
-  <si>
     <t>包主导头</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>0xEB90</t>
-  </si>
-  <si>
-    <t>版本+类型+副导头+APID</t>
-  </si>
-  <si>
-    <t>0x0520</t>
-  </si>
-  <si>
     <t>数据域长度</t>
   </si>
   <si>
@@ -370,10 +328,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>阴极点火时长上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>包主导头（不含标识符）和数据域单字节累加求和取反，取低16</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -382,14 +336,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>源包序列号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0x00~0x3FFF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -402,15 +348,206 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>初始值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>取值范围</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0x03FE</t>
+    <t>值类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字节序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小数位数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>转换方式</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE754格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE755格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE756格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE757格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE758格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE759格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE760格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE761格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE762格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE763格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE764格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE765格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE766格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE767格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE768格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE769格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE770格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE771格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE772格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE773格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE774格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE775格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE776格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE777格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE778格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE779格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE780格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE781格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE782格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE783格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE784格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE785格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE786格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE787格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE788格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE789格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE790格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE791格式</t>
+  </si>
+  <si>
+    <t>高字节在前，浮点数IEEE792格式</t>
+  </si>
+  <si>
+    <t>big_endian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位偏移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始值(HEX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EB90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0520</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源包序列计数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03FE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -418,7 +555,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,6 +600,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -483,7 +627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -536,11 +680,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -557,6 +712,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,13 +1005,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7C44AD1-3C73-47CA-A849-E82308345D6F}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="34.9140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,46 +1023,48 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3">
         <v>0.20159376000000001</v>
       </c>
-      <c r="E2">
-        <f>INT(F2/8)-8</f>
-        <v>2</v>
+      <c r="E2" t="s">
+        <v>102</v>
       </c>
       <c r="F2">
         <v>80</v>
@@ -903,31 +1073,33 @@
         <v>32</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3">
         <v>0.27821319999999999</v>
       </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E40" si="0">INT(F3/8)-8</f>
-        <v>6</v>
+      <c r="E3" t="s">
+        <v>102</v>
       </c>
       <c r="F3">
         <f>F2+G2</f>
@@ -937,1271 +1109,1348 @@
         <v>32</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3">
         <v>1.3423967000000001</v>
       </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>10</v>
+      <c r="E4" t="s">
+        <v>102</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F40" si="1">F3+G3</f>
+        <f t="shared" ref="F4:F40" si="0">F3+G3</f>
         <v>144</v>
       </c>
       <c r="G4">
         <v>32</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
         <v>41.063569999999999</v>
       </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>14</v>
+      <c r="E5" t="s">
+        <v>102</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>176</v>
       </c>
       <c r="G5">
         <v>32</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3">
         <v>0.87567099999999998</v>
       </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>18</v>
+      <c r="E6" t="s">
+        <v>102</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>208</v>
       </c>
       <c r="G6">
         <v>32</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="3">
         <v>0.13674500000000001</v>
       </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>22</v>
+      <c r="E7" t="s">
+        <v>102</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
       <c r="G7">
         <v>32</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>26</v>
+      <c r="E8" t="s">
+        <v>102</v>
       </c>
       <c r="F8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>272</v>
       </c>
       <c r="G8">
         <v>32</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
         <v>-0.96063279999999995</v>
       </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>30</v>
+      <c r="E9" t="s">
+        <v>102</v>
       </c>
       <c r="F9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>304</v>
       </c>
       <c r="G9">
         <v>32</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3">
         <v>121.86794</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>34</v>
+      <c r="E10" t="s">
+        <v>102</v>
       </c>
       <c r="F10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>336</v>
       </c>
       <c r="G10">
         <v>32</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="3">
         <v>1476.6822999999999</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>38</v>
+      <c r="E11" t="s">
+        <v>102</v>
       </c>
       <c r="F11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>368</v>
       </c>
       <c r="G11">
         <v>32</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>42</v>
+      <c r="E12" t="s">
+        <v>102</v>
       </c>
       <c r="F12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="G12">
         <v>32</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>46</v>
+      <c r="E13" t="s">
+        <v>102</v>
       </c>
       <c r="F13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>432</v>
       </c>
       <c r="G13">
         <v>32</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>50</v>
+      <c r="E14" t="s">
+        <v>102</v>
       </c>
       <c r="F14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>464</v>
       </c>
       <c r="G14">
         <v>32</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3">
         <v>0.1</v>
       </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>54</v>
+      <c r="E15" t="s">
+        <v>102</v>
       </c>
       <c r="F15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>496</v>
       </c>
       <c r="G15">
         <v>32</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3">
         <v>0.9</v>
       </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>58</v>
+      <c r="E16" t="s">
+        <v>102</v>
       </c>
       <c r="F16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>528</v>
       </c>
       <c r="G16">
         <v>32</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I16" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>62</v>
+      <c r="E17" t="s">
+        <v>102</v>
       </c>
       <c r="F17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>560</v>
       </c>
       <c r="G17">
         <v>32</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I17" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" s="3">
         <v>0.3</v>
       </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>66</v>
+      <c r="E18" t="s">
+        <v>102</v>
       </c>
       <c r="F18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>592</v>
       </c>
       <c r="G18">
         <v>32</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" s="3">
         <v>0.4</v>
       </c>
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>70</v>
+      <c r="E19" t="s">
+        <v>102</v>
       </c>
       <c r="F19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>624</v>
       </c>
       <c r="G19">
         <v>32</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D20" s="3">
         <v>560</v>
       </c>
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>74</v>
+      <c r="E20" t="s">
+        <v>102</v>
       </c>
       <c r="F20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>656</v>
       </c>
       <c r="G20">
         <v>32</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I20" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3">
         <v>120</v>
       </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>78</v>
+      <c r="E21" t="s">
+        <v>102</v>
       </c>
       <c r="F21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>688</v>
       </c>
       <c r="G21">
         <v>32</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3">
         <v>1.7</v>
       </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>82</v>
+      <c r="E22" t="s">
+        <v>102</v>
       </c>
       <c r="F22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
       <c r="G22">
         <v>32</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" s="3">
         <v>0.4</v>
       </c>
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>86</v>
+      <c r="E23" t="s">
+        <v>102</v>
       </c>
       <c r="F23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>752</v>
       </c>
       <c r="G23">
         <v>32</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="3">
         <v>0.8</v>
       </c>
-      <c r="E24">
-        <f t="shared" si="0"/>
-        <v>90</v>
+      <c r="E24" t="s">
+        <v>102</v>
       </c>
       <c r="F24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>784</v>
       </c>
       <c r="G24">
         <v>32</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J24">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" s="3">
         <v>1.5</v>
       </c>
-      <c r="E25">
-        <f t="shared" si="0"/>
-        <v>94</v>
+      <c r="E25" t="s">
+        <v>102</v>
       </c>
       <c r="F25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>816</v>
       </c>
       <c r="G25">
         <v>32</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J25">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
       </c>
-      <c r="E26">
-        <f t="shared" si="0"/>
-        <v>98</v>
+      <c r="E26" t="s">
+        <v>102</v>
       </c>
       <c r="F26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>848</v>
       </c>
       <c r="G26">
         <v>32</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J26">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="3">
         <v>2.5</v>
       </c>
-      <c r="E27">
-        <f t="shared" si="0"/>
+      <c r="E27" t="s">
         <v>102</v>
       </c>
       <c r="F27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>880</v>
       </c>
       <c r="G27">
         <v>32</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J27">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28" s="3">
         <v>2.9</v>
       </c>
-      <c r="E28">
-        <f t="shared" si="0"/>
-        <v>106</v>
+      <c r="E28" t="s">
+        <v>102</v>
       </c>
       <c r="F28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>912</v>
       </c>
       <c r="G28">
         <v>32</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I28" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J28">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="3">
         <v>3.2</v>
       </c>
-      <c r="E29">
-        <f t="shared" si="0"/>
-        <v>110</v>
+      <c r="E29" t="s">
+        <v>102</v>
       </c>
       <c r="F29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>944</v>
       </c>
       <c r="G29">
         <v>32</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J29">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="3">
         <v>3.5</v>
       </c>
-      <c r="E30">
-        <f t="shared" si="0"/>
-        <v>114</v>
+      <c r="E30" t="s">
+        <v>102</v>
       </c>
       <c r="F30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>976</v>
       </c>
       <c r="G30">
         <v>32</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J30">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="3">
         <v>280</v>
       </c>
-      <c r="E31">
-        <f t="shared" si="0"/>
-        <v>118</v>
+      <c r="E31" t="s">
+        <v>102</v>
       </c>
       <c r="F31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="G31">
         <v>32</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I31" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" s="3">
         <v>250</v>
       </c>
-      <c r="E32">
-        <f t="shared" si="0"/>
-        <v>122</v>
+      <c r="E32" t="s">
+        <v>102</v>
       </c>
       <c r="F32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="G32">
         <v>32</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J32">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D33" s="3">
         <v>1.8</v>
       </c>
-      <c r="E33">
-        <f t="shared" si="0"/>
-        <v>126</v>
+      <c r="E33" t="s">
+        <v>102</v>
       </c>
       <c r="F33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1072</v>
       </c>
       <c r="G33">
         <v>32</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J33">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L33" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D34" s="3">
         <v>0.12</v>
       </c>
-      <c r="E34">
-        <f t="shared" si="0"/>
-        <v>130</v>
+      <c r="E34" t="s">
+        <v>102</v>
       </c>
       <c r="F34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1104</v>
       </c>
       <c r="G34">
         <v>32</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J34">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D35" s="3">
         <v>40</v>
       </c>
-      <c r="E35">
-        <f t="shared" si="0"/>
-        <v>134</v>
+      <c r="E35" t="s">
+        <v>102</v>
       </c>
       <c r="F35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1136</v>
       </c>
       <c r="G35">
         <v>32</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J35">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D36" s="3">
         <v>10</v>
       </c>
-      <c r="E36">
-        <f t="shared" si="0"/>
-        <v>138</v>
+      <c r="E36" t="s">
+        <v>102</v>
       </c>
       <c r="F36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1168</v>
       </c>
       <c r="G36">
         <v>32</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37" s="3">
         <v>2</v>
       </c>
-      <c r="E37">
-        <f t="shared" si="0"/>
-        <v>142</v>
+      <c r="E37" t="s">
+        <v>102</v>
       </c>
       <c r="F37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="G37">
         <v>32</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J37">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D38" s="3">
         <v>0.3</v>
       </c>
-      <c r="E38">
-        <f t="shared" si="0"/>
-        <v>146</v>
+      <c r="E38" t="s">
+        <v>102</v>
       </c>
       <c r="F38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1232</v>
       </c>
       <c r="G38">
         <v>32</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I38" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D39" s="3">
         <v>0.3</v>
       </c>
-      <c r="E39">
-        <f t="shared" si="0"/>
-        <v>150</v>
+      <c r="E39" t="s">
+        <v>102</v>
       </c>
       <c r="F39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1264</v>
       </c>
       <c r="G39">
         <v>32</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J39">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
       </c>
-      <c r="E40">
-        <f t="shared" si="0"/>
-        <v>154</v>
+      <c r="E40" t="s">
+        <v>102</v>
       </c>
       <c r="F40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1296</v>
       </c>
       <c r="G40">
         <v>32</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I40" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="J40">
         <v>3</v>
+      </c>
+      <c r="L40" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2212,97 +2461,113 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B726021C-BBBE-4B63-A01A-6D6DD3B2E202}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="5" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="7" width="36.08203125" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="4" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="36.08203125" customWidth="1"/>
+    <col min="7" max="7" width="20.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="5">
+        <f>C2+D2</f>
+        <v>16</v>
+      </c>
+      <c r="D3" s="5">
+        <v>16</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
-        <v>109</v>
+      <c r="C4" s="5">
+        <f t="shared" ref="C4:C10" si="0">C3+D3</f>
+        <v>32</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>111</v>
+      <c r="E4" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="s">
-        <v>110</v>
+    <row r="5" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="5">
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="D5" s="5">
         <v>14</v>
@@ -2311,54 +2576,65 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="5">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>117</v>
+      <c r="A7" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="5">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="D7" s="5">
+        <v>16</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>107</v>
+        <v>155</v>
+      </c>
+      <c r="C8" s="5">
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
       <c r="D8" s="5">
         <v>32</v>
@@ -2367,17 +2643,42 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" ht="28" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="5"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="5">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+      <c r="D9" s="5">
+        <v>32</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>108</v>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="shared" si="0"/>
+        <v>144</v>
+      </c>
+      <c r="D10" s="5">
+        <v>16</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
